--- a/programs/3-day-minimum/access-62d158aa73/VOLTR-3-Day-Minimum.xlsx
+++ b/programs/3-day-minimum/access-62d158aa73/VOLTR-3-Day-Minimum.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Trained adults, at least one year of consistent lifting, whose time is limited by work and travel. You want to keep building strength and muscle on three sessions a week and you need a plan that works on the road with no adjustment.</t>
+          <t>Trained adults, at least one year of consistent lifting, whose time is limited by work and travel. You want your strength to keep moving forward on three sessions a week, and you need a plan that works on the road with one simple rule for hotel weeks.</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
 The PROGRAM tab shows the three days as rows and the eight weeks as column groups. Each week has two columns: the target and an empty Load column for you.
 Target format: sets x reps @ RIR. 3 x 6-8 @ RIR 2 means three sets of six to eight reps, each set ending with two reps in reserve. /side means each arm or leg.
 Exercises are done in pairs: one set of 1a, rest as listed on the 1a line, one set of 1b, rest as listed on the 1b line, repeat for all sets. Then pair 2, then pair 3.
-Hotel / DB alternative: use it when the equipment is missing. Take hotel sets to RIR 0 to 1, up to about 30 reps: light weights still work when the set is hard. Write H in front of the load, for example H 2 x 24, and do not use H sets to progress your barbell loads.</t>
+Hotel / DB alternative: use it when the equipment is missing. Take hotel sets to RIR 0 to 1, up to about 20 reps: light weights still work when the set is hard. Write H in front of the load, for example H 2 x 24, and do not use H sets to progress your barbell loads.</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
 Week 4: pivot week. Same exercises, two sets each, RIR 3. About 30 minutes. Fatigue drops before the harder half.
 Weeks 5 to 7: RIR 2 to 1, and the main pair gets a fourth set. Week 8 drops back to three sets so the benchmarks are tested fresh.
 After week 8: one pivot week like week 4, then start again at week 1 with your new loads.
-Hotel dumbbells too light: more reps, up to about 30, every set to RIR 0 to 1. Log it with H.</t>
+Hotel dumbbells too light: more reps, up to about 20, every set to RIR 0 to 1. Log it with H.</t>
         </is>
       </c>
     </row>
@@ -897,11 +897,12 @@
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://calendly.com/training-voltr/30min</t>
+          <t>1:1 coaching builds the program around your schedule, travel and training history. Book a 30-minute call: https://voltr.at/#book</t>
         </is>
       </c>
       <c r="D17" s="7" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="22" customHeight="1">
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1174,7 +1175,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>Rear-foot-elevated split squat with DBs, each set to RIR 0-1</t>
+          <t>Goblet squat with the heaviest DB, 3 s lowering, each set to RIR 0-1</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -1394,17 +1395,17 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Romanian deadlift</t>
+          <t>Romanian deadlift (DB or barbell)</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>DB Romanian deadlift, each set to RIR 0-1</t>
+          <t>DB Romanian deadlift, each set to RIR 1-2</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>Soft knees, hips back, weight close to the legs. Stop before the back rounds.</t>
+          <t>Soft knees, hips back, weight close to the legs. Stop before the back rounds. Use DBs if the barbell is set up for the bench.</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -2492,6 +2493,7 @@
       </c>
       <c r="U28" s="28" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -2563,6 +2565,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="31" t="inlineStr">
         <is>
@@ -2667,6 +2670,8 @@
       <c r="G14" s="34" t="n"/>
       <c r="H14" s="34" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="31" t="inlineStr">
         <is>
@@ -2768,9 +2773,11 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="22" customHeight="1">
       <c r="B26" s="10" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="B28" s="31" t="inlineStr">
         <is>
@@ -2912,6 +2919,7 @@
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="46" t="inlineStr">
         <is>
